--- a/outputs/267-21.xlsx
+++ b/outputs/267-21.xlsx
@@ -182,28 +182,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -459,95 +463,95 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="31.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="31.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>45</v>
       </c>
     </row>
@@ -570,106 +574,106 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="34.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>70</v>
       </c>
     </row>
@@ -692,162 +696,162 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>16</v>
       </c>
     </row>
